--- a/dama/cases/营收系统数据标准/2 服务类/2.2 客户管理数据/2.2.2 客户业务变更/1. 更名过户.xlsx
+++ b/dama/cases/营收系统数据标准/2 服务类/2.2 客户管理数据/2.2.2 客户业务变更/1. 更名过户.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1730" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1730" uniqueCount="391">
   <si>
     <t>业务属性</t>
   </si>
@@ -341,9 +341,6 @@
   </si>
   <si>
     <t>详细文本格式，非空</t>
-  </si>
-  <si>
-    <t>NVARCHAR2</t>
   </si>
   <si>
     <t>支持中文、自由文本</t>
@@ -1202,14 +1199,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1814,46 +1804,49 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1865,123 +1858,126 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1995,10 +1991,7 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2007,7 +2000,10 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2022,37 +2018,31 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2983,13 +2973,13 @@
         <v>77</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="Q7" s="7" t="s">
         <v>79</v>
       </c>
       <c r="R7" s="7">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="S7" s="7" t="s">
         <v>75</v>
@@ -3013,7 +3003,7 @@
         <v>83</v>
       </c>
       <c r="Z7" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AA7" s="8" t="s">
         <v>85</v>
@@ -3022,21 +3012,21 @@
         <v>86</v>
       </c>
       <c r="AC7" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD7" s="28" t="s">
         <v>111</v>
-      </c>
-      <c r="AD7" s="28" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:30">
       <c r="A8" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>114</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>115</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>69</v>
@@ -3051,10 +3041,10 @@
         <v>72</v>
       </c>
       <c r="H8" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="I8" s="6" t="s">
         <v>116</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>117</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>75</v>
@@ -3108,27 +3098,27 @@
         <v>84</v>
       </c>
       <c r="AA8" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AB8" s="5" t="s">
         <v>86</v>
       </c>
       <c r="AC8" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD8" s="28" t="s">
         <v>111</v>
-      </c>
-      <c r="AD8" s="28" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:30">
       <c r="A9" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>120</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>121</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>69</v>
@@ -3143,10 +3133,10 @@
         <v>72</v>
       </c>
       <c r="H9" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="I9" s="8" t="s">
         <v>122</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>123</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>75</v>
@@ -3197,30 +3187,30 @@
         <v>83</v>
       </c>
       <c r="Z9" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="AA9" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="AB9" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="AA9" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="AB9" s="7" t="s">
-        <v>125</v>
-      </c>
       <c r="AC9" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD9" s="28" t="s">
         <v>111</v>
-      </c>
-      <c r="AD9" s="28" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:30">
       <c r="A10" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>127</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>128</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>69</v>
@@ -3235,10 +3225,10 @@
         <v>72</v>
       </c>
       <c r="H10" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="I10" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>75</v>
@@ -3259,13 +3249,13 @@
         <v>77</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="Q10" s="5" t="s">
         <v>79</v>
       </c>
       <c r="R10" s="5">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="S10" s="5" t="s">
         <v>75</v>
@@ -3289,7 +3279,7 @@
         <v>83</v>
       </c>
       <c r="Z10" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AA10" s="6" t="s">
         <v>85</v>
@@ -3298,21 +3288,21 @@
         <v>86</v>
       </c>
       <c r="AC10" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD10" s="28" t="s">
         <v>111</v>
-      </c>
-      <c r="AD10" s="28" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:30">
       <c r="A11" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>132</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>133</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>69</v>
@@ -3327,10 +3317,10 @@
         <v>72</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J11" s="8" t="s">
         <v>75</v>
@@ -3351,13 +3341,13 @@
         <v>77</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="Q11" s="7" t="s">
         <v>79</v>
       </c>
       <c r="R11" s="7">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="S11" s="7" t="s">
         <v>75</v>
@@ -3381,7 +3371,7 @@
         <v>83</v>
       </c>
       <c r="Z11" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AA11" s="8" t="s">
         <v>85</v>
@@ -3390,21 +3380,21 @@
         <v>86</v>
       </c>
       <c r="AC11" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD11" s="28" t="s">
         <v>111</v>
-      </c>
-      <c r="AD11" s="28" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:30">
       <c r="A12" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>136</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>137</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>69</v>
@@ -3419,10 +3409,10 @@
         <v>72</v>
       </c>
       <c r="H12" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="I12" s="6" t="s">
         <v>138</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>139</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>75</v>
@@ -3443,13 +3433,13 @@
         <v>77</v>
       </c>
       <c r="P12" s="5" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="Q12" s="5" t="s">
         <v>79</v>
       </c>
       <c r="R12" s="5">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="S12" s="5" t="s">
         <v>75</v>
@@ -3473,30 +3463,30 @@
         <v>83</v>
       </c>
       <c r="Z12" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AA12" s="6" t="s">
         <v>85</v>
       </c>
       <c r="AB12" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC12" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD12" s="28" t="s">
         <v>111</v>
-      </c>
-      <c r="AD12" s="28" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:30">
       <c r="A13" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>141</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>142</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>69</v>
@@ -3511,10 +3501,10 @@
         <v>72</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J13" s="8" t="s">
         <v>75</v>
@@ -3535,13 +3525,13 @@
         <v>77</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="Q13" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="R13" s="7">
-        <v>200</v>
+      <c r="R13" s="5">
+        <v>400</v>
       </c>
       <c r="S13" s="7" t="s">
         <v>75</v>
@@ -3565,30 +3555,30 @@
         <v>83</v>
       </c>
       <c r="Z13" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AA13" s="8" t="s">
         <v>85</v>
       </c>
       <c r="AB13" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC13" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD13" s="28" t="s">
         <v>111</v>
-      </c>
-      <c r="AD13" s="28" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:30">
       <c r="A14" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="C14" s="5" t="s">
         <v>145</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>146</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>69</v>
@@ -3603,10 +3593,10 @@
         <v>72</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>75</v>
@@ -3627,7 +3617,7 @@
         <v>77</v>
       </c>
       <c r="P14" s="5" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="Q14" s="5" t="s">
         <v>79</v>
@@ -3657,30 +3647,30 @@
         <v>83</v>
       </c>
       <c r="Z14" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AA14" s="6" t="s">
         <v>85</v>
       </c>
       <c r="AB14" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC14" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="AD14" s="31" t="s">
         <v>149</v>
-      </c>
-      <c r="AD14" s="31" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:30">
       <c r="A15" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>152</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>153</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>69</v>
@@ -3695,10 +3685,10 @@
         <v>72</v>
       </c>
       <c r="H15" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="I15" s="8" t="s">
         <v>154</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>155</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>75</v>
@@ -3749,30 +3739,30 @@
         <v>83</v>
       </c>
       <c r="Z15" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AA15" s="8" t="s">
         <v>85</v>
       </c>
       <c r="AB15" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC15" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="AD15" s="31" t="s">
         <v>149</v>
-      </c>
-      <c r="AD15" s="31" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:30">
       <c r="A16" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>158</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>159</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>69</v>
@@ -3787,10 +3777,10 @@
         <v>72</v>
       </c>
       <c r="H16" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I16" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>75</v>
@@ -3844,10 +3834,10 @@
         <v>96</v>
       </c>
       <c r="AA16" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AB16" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC16" s="24" t="s">
         <v>87</v>
@@ -3858,13 +3848,13 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:30">
       <c r="A17" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>164</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>165</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>69</v>
@@ -3879,10 +3869,10 @@
         <v>72</v>
       </c>
       <c r="H17" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="I17" s="8" t="s">
         <v>166</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>167</v>
       </c>
       <c r="J17" s="8" t="s">
         <v>75</v>
@@ -3933,30 +3923,30 @@
         <v>83</v>
       </c>
       <c r="Z17" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AA17" s="8" t="s">
         <v>85</v>
       </c>
       <c r="AB17" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC17" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="AD17" s="31" t="s">
         <v>149</v>
-      </c>
-      <c r="AD17" s="31" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:30">
       <c r="A18" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="C18" s="5" t="s">
         <v>170</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>171</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>69</v>
@@ -3971,10 +3961,10 @@
         <v>72</v>
       </c>
       <c r="H18" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="I18" s="6" t="s">
         <v>172</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>173</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>75</v>
@@ -4028,10 +4018,10 @@
         <v>96</v>
       </c>
       <c r="AA18" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AB18" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC18" s="24" t="s">
         <v>87</v>
@@ -4042,13 +4032,13 @@
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:30">
       <c r="A19" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="B19" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="C19" s="7" t="s">
         <v>176</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>177</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>69</v>
@@ -4063,10 +4053,10 @@
         <v>72</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J19" s="8" t="s">
         <v>75</v>
@@ -4120,10 +4110,10 @@
         <v>96</v>
       </c>
       <c r="AA19" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AB19" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC19" s="26" t="s">
         <v>87</v>
@@ -4134,13 +4124,13 @@
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:30">
       <c r="A20" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="C20" s="5" t="s">
         <v>180</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>181</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>69</v>
@@ -4155,10 +4145,10 @@
         <v>72</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>75</v>
@@ -4179,13 +4169,13 @@
         <v>77</v>
       </c>
       <c r="P20" s="5" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="Q20" s="5" t="s">
         <v>79</v>
       </c>
       <c r="R20" s="5">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S20" s="5" t="s">
         <v>75</v>
@@ -4209,7 +4199,7 @@
         <v>83</v>
       </c>
       <c r="Z20" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AA20" s="6" t="s">
         <v>85</v>
@@ -4218,21 +4208,21 @@
         <v>86</v>
       </c>
       <c r="AC20" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD20" s="28" t="s">
         <v>111</v>
-      </c>
-      <c r="AD20" s="28" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:30">
       <c r="A21" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>184</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>185</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>69</v>
@@ -4247,10 +4237,10 @@
         <v>72</v>
       </c>
       <c r="H21" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="I21" s="8" t="s">
         <v>186</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>187</v>
       </c>
       <c r="J21" s="8" t="s">
         <v>75</v>
@@ -4304,7 +4294,7 @@
         <v>96</v>
       </c>
       <c r="AA21" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AB21" s="7" t="s">
         <v>86</v>
@@ -4318,13 +4308,13 @@
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:30">
       <c r="A22" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="C22" s="5" t="s">
         <v>190</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>191</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>69</v>
@@ -4339,10 +4329,10 @@
         <v>72</v>
       </c>
       <c r="H22" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="I22" s="6" t="s">
         <v>192</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>193</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>75</v>
@@ -4363,10 +4353,10 @@
         <v>77</v>
       </c>
       <c r="P22" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q22" s="5" t="s">
         <v>194</v>
-      </c>
-      <c r="Q22" s="5" t="s">
-        <v>195</v>
       </c>
       <c r="R22" s="5">
         <v>7</v>
@@ -4393,10 +4383,10 @@
         <v>83</v>
       </c>
       <c r="Z22" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="AA22" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="AA22" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="AB22" s="5" t="s">
         <v>86</v>
@@ -4410,13 +4400,13 @@
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:30">
       <c r="A23" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="B23" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>199</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>200</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>69</v>
@@ -4431,10 +4421,10 @@
         <v>72</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J23" s="8" t="s">
         <v>75</v>
@@ -4485,30 +4475,30 @@
         <v>83</v>
       </c>
       <c r="Z23" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AA23" s="8" t="s">
         <v>85</v>
       </c>
       <c r="AB23" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC23" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="AD23" s="31" t="s">
         <v>149</v>
-      </c>
-      <c r="AD23" s="31" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:30">
       <c r="A24" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="C24" s="5" t="s">
         <v>204</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>205</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>69</v>
@@ -4523,10 +4513,10 @@
         <v>72</v>
       </c>
       <c r="H24" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="I24" s="6" t="s">
         <v>206</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>207</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>75</v>
@@ -4577,30 +4567,30 @@
         <v>83</v>
       </c>
       <c r="Z24" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AA24" s="6" t="s">
         <v>85</v>
       </c>
       <c r="AB24" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC24" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="AD24" s="31" t="s">
         <v>149</v>
-      </c>
-      <c r="AD24" s="31" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:30">
       <c r="A25" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="B25" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="C25" s="7" t="s">
         <v>210</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>211</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>69</v>
@@ -4615,10 +4605,10 @@
         <v>72</v>
       </c>
       <c r="H25" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="I25" s="8" t="s">
         <v>212</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>213</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>75</v>
@@ -4672,7 +4662,7 @@
         <v>96</v>
       </c>
       <c r="AA25" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AB25" s="7" t="s">
         <v>86</v>
@@ -4686,13 +4676,13 @@
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:30">
       <c r="A26" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="C26" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>69</v>
@@ -4707,10 +4697,10 @@
         <v>72</v>
       </c>
       <c r="H26" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="I26" s="6" t="s">
         <v>218</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>219</v>
       </c>
       <c r="J26" s="6" t="s">
         <v>75</v>
@@ -4731,10 +4721,10 @@
         <v>77</v>
       </c>
       <c r="P26" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q26" s="5" t="s">
         <v>194</v>
-      </c>
-      <c r="Q26" s="5" t="s">
-        <v>195</v>
       </c>
       <c r="R26" s="5">
         <v>7</v>
@@ -4761,10 +4751,10 @@
         <v>83</v>
       </c>
       <c r="Z26" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="AA26" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="AA26" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="AB26" s="5" t="s">
         <v>86</v>
@@ -4778,13 +4768,13 @@
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:30">
       <c r="A27" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="B27" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="C27" s="7" t="s">
         <v>221</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>222</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>69</v>
@@ -4799,10 +4789,10 @@
         <v>72</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J27" s="8" t="s">
         <v>75</v>
@@ -4856,7 +4846,7 @@
         <v>96</v>
       </c>
       <c r="AA27" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AB27" s="7" t="s">
         <v>86</v>
@@ -4870,13 +4860,13 @@
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:30">
       <c r="A28" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="C28" s="5" t="s">
         <v>225</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>226</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>69</v>
@@ -4891,10 +4881,10 @@
         <v>72</v>
       </c>
       <c r="H28" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="I28" s="6" t="s">
         <v>227</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>228</v>
       </c>
       <c r="J28" s="6" t="s">
         <v>75</v>
@@ -4915,10 +4905,10 @@
         <v>77</v>
       </c>
       <c r="P28" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q28" s="5" t="s">
         <v>194</v>
-      </c>
-      <c r="Q28" s="5" t="s">
-        <v>195</v>
       </c>
       <c r="R28" s="5">
         <v>7</v>
@@ -4945,10 +4935,10 @@
         <v>83</v>
       </c>
       <c r="Z28" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="AA28" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="AA28" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="AB28" s="5" t="s">
         <v>86</v>
@@ -4962,13 +4952,13 @@
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:30">
       <c r="A29" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="B29" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="C29" s="7" t="s">
         <v>230</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>231</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>69</v>
@@ -4983,10 +4973,10 @@
         <v>72</v>
       </c>
       <c r="H29" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="I29" s="8" t="s">
         <v>232</v>
-      </c>
-      <c r="I29" s="8" t="s">
-        <v>233</v>
       </c>
       <c r="J29" s="8" t="s">
         <v>75</v>
@@ -5040,7 +5030,7 @@
         <v>96</v>
       </c>
       <c r="AA29" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AB29" s="7" t="s">
         <v>86</v>
@@ -5054,13 +5044,13 @@
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:30">
       <c r="A30" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="C30" s="5" t="s">
         <v>236</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>237</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>69</v>
@@ -5075,10 +5065,10 @@
         <v>72</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J30" s="6" t="s">
         <v>75</v>
@@ -5099,13 +5089,13 @@
         <v>77</v>
       </c>
       <c r="P30" s="5" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="Q30" s="5" t="s">
         <v>79</v>
       </c>
       <c r="R30" s="5">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="S30" s="5" t="s">
         <v>75</v>
@@ -5129,30 +5119,30 @@
         <v>83</v>
       </c>
       <c r="Z30" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AA30" s="6" t="s">
         <v>85</v>
       </c>
       <c r="AB30" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC30" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD30" s="28" t="s">
         <v>111</v>
-      </c>
-      <c r="AD30" s="28" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:30">
       <c r="A31" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B31" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="C31" s="7" t="s">
         <v>240</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>241</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>69</v>
@@ -5167,10 +5157,10 @@
         <v>72</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J31" s="8" t="s">
         <v>75</v>
@@ -5191,13 +5181,13 @@
         <v>77</v>
       </c>
       <c r="P31" s="7" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="Q31" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="R31" s="7">
-        <v>200</v>
+      <c r="R31" s="5">
+        <v>400</v>
       </c>
       <c r="S31" s="7" t="s">
         <v>75</v>
@@ -5221,30 +5211,30 @@
         <v>83</v>
       </c>
       <c r="Z31" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AA31" s="8" t="s">
         <v>85</v>
       </c>
       <c r="AB31" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC31" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD31" s="28" t="s">
         <v>111</v>
-      </c>
-      <c r="AD31" s="28" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1" spans="1:30">
       <c r="A32" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="C32" s="5" t="s">
         <v>244</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>245</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>69</v>
@@ -5259,10 +5249,10 @@
         <v>72</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J32" s="6" t="s">
         <v>75</v>
@@ -5283,7 +5273,7 @@
         <v>77</v>
       </c>
       <c r="P32" s="5" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="Q32" s="5" t="s">
         <v>79</v>
@@ -5319,7 +5309,7 @@
         <v>85</v>
       </c>
       <c r="AB32" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC32" s="24" t="s">
         <v>87</v>
@@ -5330,13 +5320,13 @@
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:30">
       <c r="A33" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="B33" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="C33" s="7" t="s">
         <v>248</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>249</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>69</v>
@@ -5351,10 +5341,10 @@
         <v>72</v>
       </c>
       <c r="H33" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="I33" s="8" t="s">
         <v>250</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>251</v>
       </c>
       <c r="J33" s="8" t="s">
         <v>75</v>
@@ -5375,7 +5365,7 @@
         <v>77</v>
       </c>
       <c r="P33" s="7" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="Q33" s="7" t="s">
         <v>79</v>
@@ -5405,30 +5395,30 @@
         <v>83</v>
       </c>
       <c r="Z33" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AA33" s="8" t="s">
         <v>85</v>
       </c>
       <c r="AB33" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC33" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="AD33" s="31" t="s">
         <v>149</v>
-      </c>
-      <c r="AD33" s="31" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:30">
       <c r="A34" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B34" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="C34" s="5" t="s">
         <v>254</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>255</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>69</v>
@@ -5443,10 +5433,10 @@
         <v>72</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J34" s="6" t="s">
         <v>75</v>
@@ -5467,7 +5457,7 @@
         <v>77</v>
       </c>
       <c r="P34" s="5" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="Q34" s="5" t="s">
         <v>79</v>
@@ -5497,13 +5487,13 @@
         <v>83</v>
       </c>
       <c r="Z34" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AA34" s="6" t="s">
         <v>85</v>
       </c>
       <c r="AB34" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC34" s="24" t="s">
         <v>87</v>
@@ -5514,13 +5504,13 @@
     </row>
     <row r="35" ht="20" customHeight="1" spans="1:30">
       <c r="A35" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="B35" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="C35" s="7" t="s">
         <v>259</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>260</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>69</v>
@@ -5535,10 +5525,10 @@
         <v>72</v>
       </c>
       <c r="H35" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="I35" s="8" t="s">
         <v>261</v>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>262</v>
       </c>
       <c r="J35" s="8" t="s">
         <v>75</v>
@@ -5592,10 +5582,10 @@
         <v>85</v>
       </c>
       <c r="AA35" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AB35" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC35" s="26" t="s">
         <v>87</v>
@@ -5606,13 +5596,13 @@
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:30">
       <c r="A36" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="C36" s="5" t="s">
         <v>265</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>266</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>69</v>
@@ -5627,10 +5617,10 @@
         <v>72</v>
       </c>
       <c r="H36" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="I36" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="J36" s="6" t="s">
         <v>75</v>
@@ -5684,10 +5674,10 @@
         <v>96</v>
       </c>
       <c r="AA36" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AB36" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC36" s="24" t="s">
         <v>87</v>
@@ -5698,13 +5688,13 @@
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:30">
       <c r="A37" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="B37" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="C37" s="7" t="s">
         <v>271</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>272</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>69</v>
@@ -5719,10 +5709,10 @@
         <v>72</v>
       </c>
       <c r="H37" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="I37" s="8" t="s">
         <v>273</v>
-      </c>
-      <c r="I37" s="8" t="s">
-        <v>274</v>
       </c>
       <c r="J37" s="8" t="s">
         <v>75</v>
@@ -5743,7 +5733,7 @@
         <v>77</v>
       </c>
       <c r="P37" s="7" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="Q37" s="7" t="s">
         <v>79</v>
@@ -5773,13 +5763,13 @@
         <v>83</v>
       </c>
       <c r="Z37" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AA37" s="8" t="s">
         <v>85</v>
       </c>
       <c r="AB37" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC37" s="26" t="s">
         <v>87</v>
@@ -5790,13 +5780,13 @@
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:30">
       <c r="A38" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="B38" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="C38" s="5" t="s">
         <v>276</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>277</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>69</v>
@@ -5811,10 +5801,10 @@
         <v>72</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J38" s="6" t="s">
         <v>75</v>
@@ -5868,7 +5858,7 @@
         <v>96</v>
       </c>
       <c r="AA38" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AB38" s="5" t="s">
         <v>86</v>
@@ -5882,13 +5872,13 @@
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:30">
       <c r="A39" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="B39" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="C39" s="7" t="s">
         <v>280</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>281</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>69</v>
@@ -5903,10 +5893,10 @@
         <v>72</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J39" s="8" t="s">
         <v>75</v>
@@ -5927,7 +5917,7 @@
         <v>77</v>
       </c>
       <c r="P39" s="7" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="Q39" s="7" t="s">
         <v>79</v>
@@ -5957,13 +5947,13 @@
         <v>83</v>
       </c>
       <c r="Z39" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AA39" s="8" t="s">
         <v>85</v>
       </c>
       <c r="AB39" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC39" s="26" t="s">
         <v>87</v>
@@ -5974,13 +5964,13 @@
     </row>
     <row r="40" ht="20" customHeight="1" spans="1:30">
       <c r="A40" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="C40" s="5" t="s">
         <v>284</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>285</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>69</v>
@@ -5995,10 +5985,10 @@
         <v>72</v>
       </c>
       <c r="H40" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="I40" s="6" t="s">
         <v>286</v>
-      </c>
-      <c r="I40" s="6" t="s">
-        <v>287</v>
       </c>
       <c r="J40" s="6" t="s">
         <v>75</v>
@@ -6019,10 +6009,10 @@
         <v>77</v>
       </c>
       <c r="P40" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q40" s="5" t="s">
         <v>194</v>
-      </c>
-      <c r="Q40" s="5" t="s">
-        <v>195</v>
       </c>
       <c r="R40" s="5">
         <v>7</v>
@@ -6049,30 +6039,30 @@
         <v>83</v>
       </c>
       <c r="Z40" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AA40" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AB40" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC40" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="AD40" s="31" t="s">
         <v>149</v>
-      </c>
-      <c r="AD40" s="31" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1" spans="1:30">
       <c r="A41" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="B41" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="C41" s="7" t="s">
         <v>290</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>291</v>
       </c>
       <c r="D41" s="7" t="s">
         <v>69</v>
@@ -6087,10 +6077,10 @@
         <v>72</v>
       </c>
       <c r="H41" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="I41" s="8" t="s">
         <v>292</v>
-      </c>
-      <c r="I41" s="8" t="s">
-        <v>293</v>
       </c>
       <c r="J41" s="8" t="s">
         <v>75</v>
@@ -6144,10 +6134,10 @@
         <v>96</v>
       </c>
       <c r="AA41" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AB41" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC41" s="26" t="s">
         <v>87</v>
@@ -6158,13 +6148,13 @@
     </row>
     <row r="42" ht="20" customHeight="1" spans="1:30">
       <c r="A42" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="B42" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="C42" s="5" t="s">
         <v>296</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>297</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>69</v>
@@ -6179,10 +6169,10 @@
         <v>72</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J42" s="6" t="s">
         <v>75</v>
@@ -6239,7 +6229,7 @@
         <v>85</v>
       </c>
       <c r="AB42" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC42" s="24" t="s">
         <v>87</v>
@@ -6250,13 +6240,13 @@
     </row>
     <row r="43" ht="20" customHeight="1" spans="1:30">
       <c r="A43" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="B43" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="C43" s="7" t="s">
         <v>300</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>301</v>
       </c>
       <c r="D43" s="7" t="s">
         <v>69</v>
@@ -6271,10 +6261,10 @@
         <v>72</v>
       </c>
       <c r="H43" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="I43" s="8" t="s">
         <v>302</v>
-      </c>
-      <c r="I43" s="8" t="s">
-        <v>303</v>
       </c>
       <c r="J43" s="8" t="s">
         <v>75</v>
@@ -6328,7 +6318,7 @@
         <v>96</v>
       </c>
       <c r="AA43" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AB43" s="7" t="s">
         <v>86</v>
@@ -6342,13 +6332,13 @@
     </row>
     <row r="44" ht="20" customHeight="1" spans="1:30">
       <c r="A44" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="B44" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="C44" s="5" t="s">
         <v>305</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>306</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>69</v>
@@ -6363,10 +6353,10 @@
         <v>72</v>
       </c>
       <c r="H44" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="I44" s="6" t="s">
         <v>307</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>308</v>
       </c>
       <c r="J44" s="6" t="s">
         <v>75</v>
@@ -6417,10 +6407,10 @@
         <v>83</v>
       </c>
       <c r="Z44" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="AA44" s="6" t="s">
         <v>309</v>
-      </c>
-      <c r="AA44" s="6" t="s">
-        <v>310</v>
       </c>
       <c r="AB44" s="5" t="s">
         <v>86</v>
@@ -6434,13 +6424,13 @@
     </row>
     <row r="45" ht="20" customHeight="1" spans="1:30">
       <c r="A45" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="B45" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="C45" s="7" t="s">
         <v>312</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>313</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>69</v>
@@ -6455,10 +6445,10 @@
         <v>72</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J45" s="8" t="s">
         <v>75</v>
@@ -6509,10 +6499,10 @@
         <v>83</v>
       </c>
       <c r="Z45" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="AA45" s="8" t="s">
         <v>309</v>
-      </c>
-      <c r="AA45" s="8" t="s">
-        <v>310</v>
       </c>
       <c r="AB45" s="7" t="s">
         <v>86</v>
@@ -6526,13 +6516,13 @@
     </row>
     <row r="46" ht="20" customHeight="1" spans="1:30">
       <c r="A46" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="B46" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="C46" s="5" t="s">
         <v>316</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>317</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>69</v>
@@ -6547,10 +6537,10 @@
         <v>72</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J46" s="6" t="s">
         <v>75</v>
@@ -6601,10 +6591,10 @@
         <v>83</v>
       </c>
       <c r="Z46" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="AA46" s="6" t="s">
         <v>309</v>
-      </c>
-      <c r="AA46" s="6" t="s">
-        <v>310</v>
       </c>
       <c r="AB46" s="5" t="s">
         <v>86</v>
@@ -6618,13 +6608,13 @@
     </row>
     <row r="47" ht="20" customHeight="1" spans="1:30">
       <c r="A47" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="B47" s="8" t="s">
         <v>319</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="C47" s="7" t="s">
         <v>320</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>321</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>69</v>
@@ -6639,10 +6629,10 @@
         <v>72</v>
       </c>
       <c r="H47" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="I47" s="8" t="s">
         <v>322</v>
-      </c>
-      <c r="I47" s="8" t="s">
-        <v>323</v>
       </c>
       <c r="J47" s="8" t="s">
         <v>75</v>
@@ -6693,13 +6683,13 @@
         <v>83</v>
       </c>
       <c r="Z47" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="AA47" s="8" t="s">
         <v>324</v>
       </c>
-      <c r="AA47" s="8" t="s">
-        <v>325</v>
-      </c>
       <c r="AB47" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC47" s="26" t="s">
         <v>87</v>
@@ -6710,13 +6700,13 @@
     </row>
     <row r="48" ht="20" customHeight="1" spans="1:30">
       <c r="A48" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="B48" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="C48" s="5" t="s">
         <v>327</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>328</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>69</v>
@@ -6731,10 +6721,10 @@
         <v>72</v>
       </c>
       <c r="H48" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="I48" s="6" t="s">
         <v>329</v>
-      </c>
-      <c r="I48" s="6" t="s">
-        <v>330</v>
       </c>
       <c r="J48" s="6" t="s">
         <v>75</v>
@@ -6755,7 +6745,7 @@
         <v>77</v>
       </c>
       <c r="P48" s="5" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="Q48" s="5" t="s">
         <v>79</v>
@@ -6767,7 +6757,7 @@
         <v>75</v>
       </c>
       <c r="T48" s="5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="U48" s="5" t="s">
         <v>80</v>
@@ -6785,30 +6775,30 @@
         <v>83</v>
       </c>
       <c r="Z48" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AA48" s="6" t="s">
         <v>85</v>
       </c>
       <c r="AB48" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC48" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD48" s="28" t="s">
         <v>111</v>
-      </c>
-      <c r="AD48" s="28" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1" spans="1:30">
       <c r="A49" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="B49" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="C49" s="7" t="s">
         <v>333</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>334</v>
       </c>
       <c r="D49" s="7" t="s">
         <v>69</v>
@@ -6823,10 +6813,10 @@
         <v>72</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J49" s="8" t="s">
         <v>75</v>
@@ -6847,13 +6837,13 @@
         <v>77</v>
       </c>
       <c r="P49" s="7" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="Q49" s="7" t="s">
         <v>79</v>
       </c>
       <c r="R49" s="7">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S49" s="7" t="s">
         <v>75</v>
@@ -6877,30 +6867,30 @@
         <v>83</v>
       </c>
       <c r="Z49" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AA49" s="8" t="s">
         <v>85</v>
       </c>
       <c r="AB49" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC49" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD49" s="28" t="s">
         <v>111</v>
-      </c>
-      <c r="AD49" s="28" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1" spans="1:30">
       <c r="A50" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="B50" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="C50" s="5" t="s">
         <v>337</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>338</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>69</v>
@@ -6915,10 +6905,10 @@
         <v>72</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J50" s="6" t="s">
         <v>75</v>
@@ -6969,13 +6959,13 @@
         <v>83</v>
       </c>
       <c r="Z50" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AA50" s="6" t="s">
         <v>85</v>
       </c>
       <c r="AB50" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC50" s="24" t="s">
         <v>87</v>
@@ -6986,13 +6976,13 @@
     </row>
     <row r="51" ht="20" customHeight="1" spans="1:30">
       <c r="A51" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="B51" s="8" t="s">
         <v>340</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="C51" s="7" t="s">
         <v>341</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>342</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>69</v>
@@ -7007,10 +6997,10 @@
         <v>72</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J51" s="8" t="s">
         <v>75</v>
@@ -7031,7 +7021,7 @@
         <v>77</v>
       </c>
       <c r="P51" s="7" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="Q51" s="7" t="s">
         <v>79</v>
@@ -7061,13 +7051,13 @@
         <v>83</v>
       </c>
       <c r="Z51" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AA51" s="8" t="s">
         <v>85</v>
       </c>
       <c r="AB51" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC51" s="26" t="s">
         <v>87</v>
@@ -7078,13 +7068,13 @@
     </row>
     <row r="52" ht="20" customHeight="1" spans="1:30">
       <c r="A52" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="C52" s="5" t="s">
         <v>345</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>346</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>69</v>
@@ -7099,10 +7089,10 @@
         <v>72</v>
       </c>
       <c r="H52" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="I52" s="6" t="s">
         <v>347</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>348</v>
       </c>
       <c r="J52" s="6" t="s">
         <v>75</v>
@@ -7156,27 +7146,27 @@
         <v>96</v>
       </c>
       <c r="AA52" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AB52" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC52" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="AD52" s="31" t="s">
         <v>149</v>
-      </c>
-      <c r="AD52" s="31" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1" spans="1:30">
       <c r="A53" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="B53" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="B53" s="8" t="s">
+      <c r="C53" s="7" t="s">
         <v>351</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>352</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>69</v>
@@ -7191,10 +7181,10 @@
         <v>72</v>
       </c>
       <c r="H53" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="I53" s="8" t="s">
         <v>353</v>
-      </c>
-      <c r="I53" s="8" t="s">
-        <v>354</v>
       </c>
       <c r="J53" s="8" t="s">
         <v>75</v>
@@ -7215,10 +7205,10 @@
         <v>77</v>
       </c>
       <c r="P53" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q53" s="7" t="s">
         <v>194</v>
-      </c>
-      <c r="Q53" s="7" t="s">
-        <v>195</v>
       </c>
       <c r="R53" s="7">
         <v>7</v>
@@ -7245,13 +7235,13 @@
         <v>83</v>
       </c>
       <c r="Z53" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AA53" s="8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AB53" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC53" s="26" t="s">
         <v>87</v>
@@ -7262,13 +7252,13 @@
     </row>
     <row r="54" ht="20" customHeight="1" spans="1:30">
       <c r="A54" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="B54" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="C54" s="5" t="s">
         <v>356</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>357</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>69</v>
@@ -7283,10 +7273,10 @@
         <v>72</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J54" s="6" t="s">
         <v>75</v>
@@ -7337,30 +7327,30 @@
         <v>83</v>
       </c>
       <c r="Z54" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AA54" s="6" t="s">
         <v>85</v>
       </c>
       <c r="AB54" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC54" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD54" s="28" t="s">
         <v>111</v>
-      </c>
-      <c r="AD54" s="28" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1" spans="1:30">
       <c r="A55" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="B55" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="C55" s="7" t="s">
         <v>360</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>361</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>69</v>
@@ -7375,10 +7365,10 @@
         <v>72</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J55" s="8" t="s">
         <v>75</v>
@@ -7429,30 +7419,30 @@
         <v>83</v>
       </c>
       <c r="Z55" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AA55" s="8" t="s">
         <v>85</v>
       </c>
       <c r="AB55" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC55" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD55" s="28" t="s">
         <v>111</v>
-      </c>
-      <c r="AD55" s="28" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1" spans="1:30">
       <c r="A56" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="B56" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="C56" s="5" t="s">
         <v>364</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>365</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>69</v>
@@ -7467,10 +7457,10 @@
         <v>72</v>
       </c>
       <c r="H56" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="I56" s="6" t="s">
         <v>366</v>
-      </c>
-      <c r="I56" s="6" t="s">
-        <v>367</v>
       </c>
       <c r="J56" s="6" t="s">
         <v>75</v>
@@ -7524,10 +7514,10 @@
         <v>96</v>
       </c>
       <c r="AA56" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AB56" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC56" s="24" t="s">
         <v>87</v>
@@ -7538,13 +7528,13 @@
     </row>
     <row r="57" ht="20" customHeight="1" spans="1:30">
       <c r="A57" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="B57" s="8" t="s">
         <v>369</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="C57" s="7" t="s">
         <v>370</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>371</v>
       </c>
       <c r="D57" s="7" t="s">
         <v>69</v>
@@ -7559,10 +7549,10 @@
         <v>72</v>
       </c>
       <c r="H57" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="I57" s="8" t="s">
         <v>372</v>
-      </c>
-      <c r="I57" s="8" t="s">
-        <v>373</v>
       </c>
       <c r="J57" s="8" t="s">
         <v>75</v>
@@ -7613,30 +7603,30 @@
         <v>83</v>
       </c>
       <c r="Z57" s="8" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA57" s="8" t="s">
         <v>85</v>
       </c>
       <c r="AB57" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC57" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="AD57" s="31" t="s">
         <v>149</v>
-      </c>
-      <c r="AD57" s="31" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1" spans="1:30">
       <c r="A58" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B58" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="C58" s="5" t="s">
         <v>376</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>377</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>69</v>
@@ -7651,10 +7641,10 @@
         <v>72</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J58" s="6" t="s">
         <v>75</v>
@@ -7675,13 +7665,13 @@
         <v>77</v>
       </c>
       <c r="P58" s="5" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="Q58" s="5" t="s">
         <v>79</v>
       </c>
       <c r="R58" s="5">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="S58" s="5" t="s">
         <v>75</v>
@@ -7705,30 +7695,30 @@
         <v>83</v>
       </c>
       <c r="Z58" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AA58" s="6" t="s">
         <v>85</v>
       </c>
       <c r="AB58" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC58" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD58" s="28" t="s">
         <v>111</v>
-      </c>
-      <c r="AD58" s="28" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1" spans="1:30">
       <c r="A59" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="B59" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="C59" s="7" t="s">
         <v>380</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>381</v>
       </c>
       <c r="D59" s="7" t="s">
         <v>69</v>
@@ -7743,10 +7733,10 @@
         <v>72</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J59" s="8" t="s">
         <v>75</v>
@@ -7797,13 +7787,13 @@
         <v>83</v>
       </c>
       <c r="Z59" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AA59" s="8" t="s">
         <v>85</v>
       </c>
       <c r="AB59" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC59" s="26" t="s">
         <v>87</v>
@@ -7814,13 +7804,13 @@
     </row>
     <row r="60" ht="20" customHeight="1" spans="1:30">
       <c r="A60" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="B60" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="C60" s="5" t="s">
         <v>384</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>385</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>69</v>
@@ -7835,10 +7825,10 @@
         <v>72</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J60" s="6" t="s">
         <v>75</v>
@@ -7889,30 +7879,30 @@
         <v>83</v>
       </c>
       <c r="Z60" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AA60" s="6" t="s">
         <v>85</v>
       </c>
       <c r="AB60" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC60" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD60" s="28" t="s">
         <v>111</v>
-      </c>
-      <c r="AD60" s="28" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1" spans="1:30">
       <c r="A61" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="B61" s="8" t="s">
         <v>387</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="C61" s="7" t="s">
         <v>388</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>389</v>
       </c>
       <c r="D61" s="7" t="s">
         <v>69</v>
@@ -7927,10 +7917,10 @@
         <v>72</v>
       </c>
       <c r="H61" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="I61" s="8" t="s">
         <v>390</v>
-      </c>
-      <c r="I61" s="8" t="s">
-        <v>391</v>
       </c>
       <c r="J61" s="8" t="s">
         <v>75</v>
@@ -7984,7 +7974,7 @@
         <v>96</v>
       </c>
       <c r="AA61" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AB61" s="7" t="s">
         <v>86</v>
